--- a/templates/amazon_single_product_meeting_template.xlsx
+++ b/templates/amazon_single_product_meeting_template.xlsx
@@ -12,6 +12,7 @@
     <sheet name="评论VOC" sheetId="5" r:id="rId5"/>
     <sheet name="竞争策略" sheetId="6" r:id="rId6"/>
     <sheet name="数据来源" sheetId="7" r:id="rId7"/>
+    <sheet name="MCP原始数据" sheetId="8" r:id="rId8"/>
   </sheets>
 </workbook>
 </file>
@@ -957,4 +958,150 @@
   </sheetData>
   <autoFilter ref="A1:C6"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="38" customWidth="1"/>
+    <col min="5" max="5" width="70" customWidth="1"/>
+    <col min="6" max="6" width="38" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr" s="2">
+        <is>
+          <t>数据文件/接口</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr" s="2">
+        <is>
+          <t>采集时间</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr" s="2">
+        <is>
+          <t>记录序号</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr" s="2">
+        <is>
+          <t>字段路径</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr" s="2">
+        <is>
+          <t>原始值</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr" s="2">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>{{RAW_SOURCE_1}}</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>{{RAW_COLLECTED_AT_1}}</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>{{RAW_INDEX_1}}</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>{{RAW_FIELD_PATH_1}}</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>{{RAW_VALUE_1}}</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>{{RAW_NOTE_1}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>{{RAW_SOURCE_2}}</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>{{RAW_COLLECTED_AT_2}}</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>{{RAW_INDEX_2}}</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>{{RAW_FIELD_PATH_2}}</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>{{RAW_VALUE_2}}</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>{{RAW_NOTE_2}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>{{RAW_SOURCE_3}}</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>{{RAW_COLLECTED_AT_3}}</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>{{RAW_INDEX_3}}</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>{{RAW_FIELD_PATH_3}}</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>{{RAW_VALUE_3}}</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>{{RAW_NOTE_3}}</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F8"/>
+</worksheet>
 </file>